--- a/dataset/02.wo_Defects/wrong_arguments_func_pointer.xlsx
+++ b/dataset/02.wo_Defects/wrong_arguments_func_pointer.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_014 () { long arr[5]; if(wrong_arguments_func_pointer_014_func_001(0) == 0) { long (*fptr)(long [],int); long a; fptr = wrong_arguments_func_pointer_014_func_002; a =fptr(arr,5); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } } long wrong_arguments_func_pointer_014_func_002 (long a[],int max) { int i; for(i=0;i&lt;max;i++) { a[i] = i; } return a[i]; } int wrong_arguments_func_pointer_014_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_014 () { long arr[5]; if(wrong_arguments_func_pointer_014_func_001(0) == 0) { long (*fptr)(long [],int); long a; fptr = wrong_arguments_func_pointer_014_func_002; a =fptr(arr,5); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } } int wrong_arguments_func_pointer_014_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; } long wrong_arguments_func_pointer_014_func_002 (long a[],int max) { int i; for(i=0;i&lt;max;i++) { a[i] = i; } return a[i]; }</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
